--- a/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T14:16:52+00:00</t>
+    <t>2025-12-22T14:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T14:22:23+00:00</t>
+    <t>2025-12-22T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -135,37 +135,19 @@
     <t>unconfirmed</t>
   </si>
   <si>
-    <t>Obekräftad</t>
-  </si>
-  <si>
-    <t>provisional</t>
-  </si>
-  <si>
-    <t>Preliminär</t>
-  </si>
-  <si>
-    <t>differential</t>
-  </si>
-  <si>
-    <t>Differential</t>
+    <t>Non confirmé</t>
   </si>
   <si>
     <t>confirmed</t>
   </si>
   <si>
-    <t>Bekräftad</t>
+    <t>Confirmé</t>
   </si>
   <si>
     <t>refuted</t>
   </si>
   <si>
-    <t>Motbevisad</t>
-  </si>
-  <si>
-    <t>entered-in-error</t>
-  </si>
-  <si>
-    <t>Felaktigt inmatad</t>
+    <t>Réfuté</t>
   </si>
 </sst>
 </file>
@@ -467,7 +449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -520,42 +502,6 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:10:15+00:00</t>
+    <t>2025-12-22T17:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:17:12+00:00</t>
+    <t>2025-12-22T17:21:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:21:11+00:00</t>
+    <t>2025-12-22T17:32:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:32:51+00:00</t>
+    <t>2025-12-22T17:37:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:37:51+00:00</t>
+    <t>2025-12-22T17:43:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:43:16+00:00</t>
+    <t>2025-12-23T08:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-condition-ver-status.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T08:56:57+00:00</t>
+    <t>2025-12-23T09:21:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
